--- a/public/samples/rtm-format-sample.xlsx
+++ b/public/samples/rtm-format-sample.xlsx
@@ -12,8 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세부 항목 판정" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="표에 없는 요구사항" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지적 예상 목록" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="과업대비표(검토본)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검사기준서·시험결과 대응" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DB 정합" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -93,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,6 +115,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -542,7 +542,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>제안요청서(hwp, 138,945자) · 요구사항정의서(xlsx, 65행) · 화면정의서(hwp) · 프로그램명세서(hwp) · 인터페이스정의서(docx) · 요구사항추적표(xlsx, 5행 — 견본)</t>
+          <t>제안요청서(hwp, 138,945자) · 요구사항정의서(xlsx, 65행) · 화면정의서(hwp) · 프로그램명세서(hwp) · 인터페이스정의서(docx) · 테이블정의서(hwp) · 요구사항추적표(xlsx, 5행 — 견본)</t>
         </is>
       </c>
     </row>
@@ -680,46 +680,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>시험결과 대응 (TEST · 종료 회차 견본)</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>고정 문장</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>판정은 감리원의 점검 순서(형식 요건·추적성·설계 반영)를 문서만으로 먼저 수행한 예상입니다. 확정은 감리원이 합니다.</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>고정 문장</t>
+          <t>보지 않은 것</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>판정은 감리원의 점검 순서(형식 요건·추적성·설계 반영)를 문서만으로 먼저 수행한 예상입니다. 확정은 감리원이 합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>보지 않은 것</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>사업관리·DB·시스템 구조·보안 영역, 시험 수행 여부.</t>
+          <t>사업관리·시스템 구조·보안 영역, 설계 품질, 시험 수행 여부. 데이터베이스는 설계 산출물의 문서 정합만 봅니다(ERD 그림·실제 DB 대조 제외).</t>
         </is>
       </c>
     </row>
@@ -1710,330 +1691,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>요구정의 회차 — 과업대비표 원형 + 3열</t>
+          <t>DB 정합 목록 — 테이블 3 · 컬럼 5 · 표준용어: 행정안전부 공통표준단어(2025-11-01판) — 기관 표준사전을 주지 않아 기본값으로. 규칙으로 찾은 사실 목록이며 판정이 아님. 위 묶음은 감리 개선권고 틀, 아래는 행 전부</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>과업항목 ID</t>
+          <t>묶음</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>과업내용</t>
+          <t>현황 및 문제점</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>요구사항 ID</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>판정(예상)</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>근거</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>비고</t>
+          <t>개선방향</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>DB-1 · 컬럼 정의 불일치</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>데이터 수집 메타데이터 보존</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>부적합 예상</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>요구사항정의서에 대응 ID 없음</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>ROW · 과업내용이 요구사항정의서에 없음</t>
+          <t>1건. 예: 같은 컬럼ID 에 타입이 여럿: NUMBER(10) / VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>컬럼 ID·명칭·데이터 타입을 표준 도메인에 맞춰 테이블 간에 통일.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>T-05</t>
+          <t>DB-3 · 키 정의</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>외부 API 연계</t>
+          <t>3건. 예: TB_LINK_HIST: PK 로 표시된 컬럼이 없음; TB_TEMP: PK 로 표시된 컬럼이 없음; TB_TEMP: 컬럼이 하나뿐(임시값)</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>REQ-F-020</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>적합 예상</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>요구사항정의서 REQ-F-020</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>종료 회차 — 검사기준서 × 시험결과서</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>검사항목 ID</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>요구사항 ID</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>검사기준(원문)</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>시험 케이스 ID</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>결과</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>조치</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>판정(예상)</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>CK-012</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>SFR-012</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>「알림 발생 후 3초 이내 화면 표시」</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>CK-012</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>부적합 예상</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>TEST · 실패 후 조치 미기재</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>CK-015</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>SFR-015</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>「키워드·분류 검색 결과 일치」</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>CK-015</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>적합 예상</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>TEST</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>CK-020</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>SFR-020</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>「연계 이력 조회 가능」</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>부적합 예상</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>TEST · 시험 케이스 없음</t>
+          <t>테이블마다 PK 와 참여 순서를 정의하고, 컬럼이 하나뿐인 테이블은 설계 의도를 확인.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>CK-099</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>SFR-099</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>「정상 동작」</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>CK-099</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>적합 예상</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>TEST</t>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>묶음</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>검사</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>위치(테이블#행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>DB-1</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>type_conflict</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>같은 컬럼ID 에 타입이 여럿: NUMBER(10) / VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TB_DATASET#2, TB_LINK_HIST#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>DB-3</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>no_pk</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>TB_LINK_HIST: PK 로 표시된 컬럼이 없음</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TB_LINK_HIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>DB-3</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>no_pk</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>TB_TEMP: PK 로 표시된 컬럼이 없음</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TB_TEMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>DB-3</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>single_column_table</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>TB_TEMP: 컬럼이 하나뿐(임시값)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TB_TEMP</t>
         </is>
       </c>
     </row>

--- a/public/samples/rtm-format-sample.xlsx
+++ b/public/samples/rtm-format-sample.xlsx
@@ -966,12 +966,12 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>유스케이스 ID·화면 ID·컴포넌트 ID·프로그램 ID 열 비어 있음</t>
+          <t>화면 ID·컴포넌트 ID·프로그램 ID 열 비어 있음</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>FORM · 설계단계 추적 항목 미기재(유스케이스 ID·화면 ID·컴포넌트 ID·프로그램 ID)</t>
+          <t>FORM · 설계단계 추적 항목 미기재(화면 ID·컴포넌트 ID·프로그램 ID)</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>대비표의 요구사항ID별 관련 산출물 정보 작성 현황을 점검한 결과, 설계단계 추적 항목이 기재되지 않은 요구사항이 확인되므로 보완할 필요가 있음. 요구사항 1건(SFR-031)의 유스케이스 ID·화면 ID·컴포넌트 ID·프로그램 ID 열이 비어 있음.</t>
+          <t>대비표의 요구사항ID별 관련 산출물 정보 작성 현황을 점검한 결과, 설계단계 추적 항목이 기재되지 않은 요구사항이 확인되므로 보완할 필요가 있음. 요구사항 1건(SFR-031)의 화면 ID·컴포넌트 ID·프로그램 ID 열이 비어 있음.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
